--- a/Stock_Daily_Reefer_9-30.xlsx
+++ b/Stock_Daily_Reefer_9-30.xlsx
@@ -46,7 +46,6 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
-    <font/>
     <font>
       <b val="1"/>
       <color rgb="00808080"/>
@@ -66,6 +65,7 @@
       <color rgb="00EB6834"/>
       <sz val="20"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -145,10 +145,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00808080"/>
       <sz val="11"/>
@@ -168,6 +164,10 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
@@ -261,20 +261,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
@@ -288,27 +274,9 @@
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
         <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right style="thin">
         <color rgb="00BFBFBF"/>
       </right>
@@ -318,18 +286,6 @@
       <bottom style="thin">
         <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -359,6 +315,50 @@
         <color rgb="00BFBFBF"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
       <bottom style="thin">
         <color rgb="00BFBFBF"/>
       </bottom>
@@ -416,123 +416,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -540,19 +474,85 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -635,7 +635,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -6239,823 +6239,823 @@
     </row>
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>CARGO CLASSIFICATION  (40'RH stock by Built Year, per depot)</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n"/>
+      <c r="D33" s="1" t="n"/>
+      <c r="E33" s="1" t="n"/>
+      <c r="F33" s="1" t="n"/>
+      <c r="G33" s="1" t="n"/>
+      <c r="H33" s="1" t="n"/>
+      <c r="I33" s="1" t="n"/>
+      <c r="J33" s="1" t="n"/>
+      <c r="K33" s="1" t="n"/>
+      <c r="L33" s="1" t="n"/>
+      <c r="M33" s="1" t="n"/>
+      <c r="N33" s="1" t="n"/>
+      <c r="O33" s="1" t="n"/>
+      <c r="P33" s="1" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>BKK27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>BKK27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>LCH27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n"/>
+      <c r="L34" s="23" t="n"/>
+      <c r="M34" s="1" t="n"/>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>LCH27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="O34" s="23" t="n"/>
+      <c r="P34" s="23" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="24">
+        <f>SUM(D42:D47)+SUM(F42:F47)+SUM(H42:H47)</f>
+        <v/>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="1" t="n"/>
+      <c r="F35" s="24">
+        <f>SUM(D48:D58)+SUM(F48:F58)+SUM(H48:H58)</f>
+        <v/>
+      </c>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="1" t="n"/>
+      <c r="J35" s="25">
+        <f>SUM(L42:L47)+SUM(N42:N47)+SUM(P42:P47)</f>
+        <v/>
+      </c>
+      <c r="K35" s="23" t="n"/>
+      <c r="L35" s="23" t="n"/>
+      <c r="M35" s="1" t="n"/>
+      <c r="N35" s="25">
+        <f>SUM(L48:L58)+SUM(N48:N58)+SUM(P48:P58)</f>
+        <v/>
+      </c>
+      <c r="O35" s="23" t="n"/>
+      <c r="P35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="1" t="n"/>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n"/>
+      <c r="L36" s="23" t="n"/>
+      <c r="M36" s="1" t="n"/>
+      <c r="N36" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="O36" s="23" t="n"/>
+      <c r="P36" s="23" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="n"/>
+      <c r="F37" s="1" t="n"/>
+      <c r="G37" s="1" t="n"/>
+      <c r="H37" s="1" t="n"/>
+      <c r="I37" s="1" t="n"/>
+      <c r="J37" s="1" t="n"/>
+      <c r="K37" s="1" t="n"/>
+      <c r="L37" s="1" t="n"/>
+      <c r="M37" s="1" t="n"/>
+      <c r="N37" s="1" t="n"/>
+      <c r="O37" s="1" t="n"/>
+      <c r="P37" s="1" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="n"/>
+      <c r="I38" s="1" t="n"/>
+      <c r="J38" s="1" t="n"/>
+      <c r="K38" s="1" t="n"/>
+      <c r="L38" s="1" t="n"/>
+      <c r="M38" s="1" t="n"/>
+      <c r="N38" s="1" t="n"/>
+      <c r="O38" s="1" t="n"/>
+      <c r="P38" s="1" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>BKK27 / BC2  —  Stock by Built Year x Brand x Size</t>
         </is>
       </c>
-      <c r="C33" s="56" t="n"/>
-      <c r="D33" s="56" t="n"/>
-      <c r="E33" s="56" t="n"/>
-      <c r="F33" s="56" t="n"/>
-      <c r="G33" s="56" t="n"/>
-      <c r="H33" s="57" t="n"/>
-      <c r="I33" s="1" t="n"/>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="C39" s="56" t="n"/>
+      <c r="D39" s="56" t="n"/>
+      <c r="E39" s="56" t="n"/>
+      <c r="F39" s="56" t="n"/>
+      <c r="G39" s="56" t="n"/>
+      <c r="H39" s="57" t="n"/>
+      <c r="I39" s="1" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>LCH27 / HAST  —  Stock by Built Year x Brand x Size</t>
         </is>
       </c>
-      <c r="K33" s="56" t="n"/>
-      <c r="L33" s="56" t="n"/>
-      <c r="M33" s="56" t="n"/>
-      <c r="N33" s="56" t="n"/>
-      <c r="O33" s="56" t="n"/>
-      <c r="P33" s="57" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="K39" s="56" t="n"/>
+      <c r="L39" s="56" t="n"/>
+      <c r="M39" s="56" t="n"/>
+      <c r="N39" s="56" t="n"/>
+      <c r="O39" s="56" t="n"/>
+      <c r="P39" s="57" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="D34" s="57" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="D40" s="57" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="F34" s="57" t="n"/>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="F40" s="57" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="H34" s="57" t="n"/>
-      <c r="I34" s="1" t="n"/>
-      <c r="J34" s="18" t="inlineStr">
+      <c r="H40" s="57" t="n"/>
+      <c r="I40" s="1" t="n"/>
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="L34" s="57" t="n"/>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L40" s="57" t="n"/>
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="N34" s="57" t="n"/>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="N40" s="57" t="n"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="P34" s="57" t="n"/>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="60" t="n"/>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="H35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="I35" s="1" t="n"/>
-      <c r="J35" s="60" t="n"/>
-      <c r="K35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="L35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="M35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="N35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="O35" s="22" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="P35" s="22" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="1" t="n"/>
-      <c r="J36" s="23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="24" t="n"/>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
-      <c r="P36" s="24" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="1" t="n"/>
-      <c r="J37" s="23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K37" s="24" t="n"/>
-      <c r="L37" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="M37" s="24" t="n"/>
-      <c r="N37" s="24" t="n"/>
-      <c r="O37" s="24" t="n"/>
-      <c r="P37" s="24" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C38" s="24" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="n"/>
-      <c r="I38" s="1" t="n"/>
-      <c r="J38" s="23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K38" s="24" t="n"/>
-      <c r="L38" s="24" t="n"/>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="24" t="n"/>
-      <c r="O38" s="24" t="n"/>
-      <c r="P38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="23" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="1" t="n"/>
-      <c r="J39" s="23" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
-      <c r="O39" s="24" t="n"/>
-      <c r="P39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="23" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
-      <c r="G40" s="24" t="n"/>
-      <c r="H40" s="24" t="n"/>
-      <c r="I40" s="1" t="n"/>
-      <c r="J40" s="23" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K40" s="24" t="n"/>
-      <c r="L40" s="24" t="n"/>
-      <c r="M40" s="24" t="n"/>
-      <c r="N40" s="24" t="n"/>
-      <c r="O40" s="24" t="n"/>
-      <c r="P40" s="24" t="n"/>
+      <c r="P40" s="57" t="n"/>
     </row>
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C41" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="D41" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
+      <c r="B41" s="60" t="n"/>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="G41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
       <c r="I41" s="1" t="n"/>
-      <c r="J41" s="23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="K41" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="M41" s="24" t="n"/>
-      <c r="N41" s="24" t="n"/>
-      <c r="O41" s="24" t="n"/>
-      <c r="P41" s="24" t="n"/>
+      <c r="J41" s="60" t="n"/>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="L41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="M41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="N41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="O41" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="P41" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="25" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C42" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
+      <c r="B42" s="29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="30" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="30" t="n"/>
+      <c r="H42" s="30" t="n"/>
       <c r="I42" s="1" t="n"/>
-      <c r="J42" s="25" t="n">
-        <v>2020</v>
-      </c>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="26" t="n"/>
-      <c r="P42" s="26" t="n"/>
+      <c r="J42" s="29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
+      <c r="M42" s="30" t="n"/>
+      <c r="N42" s="30" t="n"/>
+      <c r="O42" s="30" t="n"/>
+      <c r="P42" s="30" t="n"/>
     </row>
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="25" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C43" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
-      <c r="G43" s="26" t="n"/>
-      <c r="H43" s="26" t="n"/>
+      <c r="B43" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="30" t="n"/>
+      <c r="H43" s="30" t="n"/>
       <c r="I43" s="1" t="n"/>
-      <c r="J43" s="25" t="n">
-        <v>2019</v>
-      </c>
-      <c r="K43" s="26" t="n"/>
-      <c r="L43" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="M43" s="26" t="n"/>
-      <c r="N43" s="26" t="n"/>
-      <c r="O43" s="26" t="n"/>
-      <c r="P43" s="26" t="n"/>
+      <c r="J43" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="M43" s="30" t="n"/>
+      <c r="N43" s="30" t="n"/>
+      <c r="O43" s="30" t="n"/>
+      <c r="P43" s="30" t="n"/>
     </row>
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="25" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C44" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="n"/>
-      <c r="H44" s="26" t="n"/>
+      <c r="B44" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="30" t="n"/>
+      <c r="E44" s="30" t="n"/>
+      <c r="F44" s="30" t="n"/>
+      <c r="G44" s="30" t="n"/>
+      <c r="H44" s="30" t="n"/>
       <c r="I44" s="1" t="n"/>
-      <c r="J44" s="25" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="M44" s="26" t="n"/>
-      <c r="N44" s="26" t="n"/>
-      <c r="O44" s="26" t="n"/>
-      <c r="P44" s="26" t="n"/>
+      <c r="J44" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
+      <c r="M44" s="30" t="n"/>
+      <c r="N44" s="30" t="n"/>
+      <c r="O44" s="30" t="n"/>
+      <c r="P44" s="30" t="n"/>
     </row>
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="25" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C45" s="26" t="n">
+      <c r="B45" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="26" t="n"/>
-      <c r="G45" s="26" t="n"/>
-      <c r="H45" s="26" t="n"/>
+      <c r="E45" s="30" t="n"/>
+      <c r="F45" s="30" t="n"/>
+      <c r="G45" s="30" t="n"/>
+      <c r="H45" s="30" t="n"/>
       <c r="I45" s="1" t="n"/>
-      <c r="J45" s="25" t="n">
-        <v>2017</v>
-      </c>
-      <c r="K45" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="26" t="n"/>
-      <c r="N45" s="26" t="n"/>
-      <c r="O45" s="26" t="n"/>
-      <c r="P45" s="26" t="n"/>
+      <c r="J45" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
+      <c r="M45" s="30" t="n"/>
+      <c r="N45" s="30" t="n"/>
+      <c r="O45" s="30" t="n"/>
+      <c r="P45" s="30" t="n"/>
     </row>
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="25" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="n"/>
+      <c r="B46" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C46" s="30" t="n"/>
+      <c r="D46" s="30" t="n"/>
+      <c r="E46" s="30" t="n"/>
+      <c r="F46" s="30" t="n"/>
+      <c r="G46" s="30" t="n"/>
+      <c r="H46" s="30" t="n"/>
       <c r="I46" s="1" t="n"/>
-      <c r="J46" s="25" t="n">
-        <v>2016</v>
-      </c>
-      <c r="K46" s="26" t="n"/>
-      <c r="L46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" s="26" t="n"/>
-      <c r="N46" s="26" t="n"/>
-      <c r="O46" s="26" t="n"/>
-      <c r="P46" s="26" t="n"/>
+      <c r="J46" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K46" s="30" t="n"/>
+      <c r="L46" s="30" t="n"/>
+      <c r="M46" s="30" t="n"/>
+      <c r="N46" s="30" t="n"/>
+      <c r="O46" s="30" t="n"/>
+      <c r="P46" s="30" t="n"/>
     </row>
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="27" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C47" s="28" t="n"/>
-      <c r="D47" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="28" t="n"/>
-      <c r="G47" s="28" t="n"/>
-      <c r="H47" s="28" t="n"/>
+      <c r="B47" s="29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
+      <c r="G47" s="30" t="n"/>
+      <c r="H47" s="30" t="n"/>
       <c r="I47" s="1" t="n"/>
-      <c r="J47" s="27" t="n">
-        <v>2015</v>
-      </c>
-      <c r="K47" s="28" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="28" t="n"/>
-      <c r="N47" s="28" t="n"/>
-      <c r="O47" s="28" t="n"/>
-      <c r="P47" s="28" t="n"/>
+      <c r="J47" s="29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K47" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="M47" s="30" t="n"/>
+      <c r="N47" s="30" t="n"/>
+      <c r="O47" s="30" t="n"/>
+      <c r="P47" s="30" t="n"/>
     </row>
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="27" t="n">
-        <v>2014</v>
-      </c>
-      <c r="C48" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="28" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="28" t="n"/>
-      <c r="G48" s="28" t="n"/>
-      <c r="H48" s="28" t="n"/>
+      <c r="B48" s="31" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="32" t="n"/>
+      <c r="F48" s="32" t="n"/>
+      <c r="G48" s="32" t="n"/>
+      <c r="H48" s="32" t="n"/>
       <c r="I48" s="1" t="n"/>
-      <c r="J48" s="27" t="n">
-        <v>2014</v>
-      </c>
-      <c r="K48" s="28" t="n"/>
-      <c r="L48" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="28" t="n"/>
-      <c r="N48" s="28" t="n"/>
-      <c r="O48" s="28" t="n"/>
-      <c r="P48" s="28" t="n"/>
+      <c r="J48" s="31" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K48" s="32" t="n"/>
+      <c r="L48" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" s="32" t="n"/>
+      <c r="N48" s="32" t="n"/>
+      <c r="O48" s="32" t="n"/>
+      <c r="P48" s="32" t="n"/>
     </row>
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="27" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C49" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="28" t="n"/>
-      <c r="E49" s="28" t="n">
+      <c r="B49" s="31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C49" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="28" t="n"/>
+      <c r="D49" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="32" t="n"/>
       <c r="I49" s="1" t="n"/>
-      <c r="J49" s="27" t="n">
-        <v>2013</v>
-      </c>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="28" t="n"/>
-      <c r="P49" s="28" t="n"/>
+      <c r="J49" s="31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K49" s="32" t="n"/>
+      <c r="L49" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" s="32" t="n"/>
+      <c r="N49" s="32" t="n"/>
+      <c r="O49" s="32" t="n"/>
+      <c r="P49" s="32" t="n"/>
     </row>
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="27" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="28" t="n"/>
-      <c r="F50" s="28" t="n"/>
-      <c r="G50" s="28" t="n"/>
-      <c r="H50" s="28" t="n"/>
+      <c r="B50" s="31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C50" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="32" t="n"/>
+      <c r="E50" s="32" t="n"/>
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="32" t="n"/>
+      <c r="H50" s="32" t="n"/>
       <c r="I50" s="1" t="n"/>
-      <c r="J50" s="27" t="n">
-        <v>2012</v>
-      </c>
-      <c r="K50" s="28" t="n"/>
-      <c r="L50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="28" t="n"/>
-      <c r="O50" s="28" t="n"/>
-      <c r="P50" s="28" t="n"/>
+      <c r="J50" s="31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K50" s="32" t="n"/>
+      <c r="L50" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" s="32" t="n"/>
+      <c r="N50" s="32" t="n"/>
+      <c r="O50" s="32" t="n"/>
+      <c r="P50" s="32" t="n"/>
     </row>
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="27" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C51" s="28" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="28" t="n"/>
+      <c r="B51" s="31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C51" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
+      <c r="H51" s="32" t="n"/>
       <c r="I51" s="1" t="n"/>
-      <c r="J51" s="27" t="n">
-        <v>2011</v>
-      </c>
-      <c r="K51" s="28" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="28" t="n"/>
-      <c r="N51" s="28" t="n">
+      <c r="J51" s="31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K51" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="O51" s="28" t="n"/>
-      <c r="P51" s="28" t="n"/>
+      <c r="L51" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="32" t="n"/>
+      <c r="N51" s="32" t="n"/>
+      <c r="O51" s="32" t="n"/>
+      <c r="P51" s="32" t="n"/>
     </row>
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="1" t="n"/>
-      <c r="B52" s="29" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="30" t="n"/>
-      <c r="F52" s="30" t="n"/>
-      <c r="G52" s="30" t="n"/>
-      <c r="H52" s="30" t="n"/>
+      <c r="B52" s="31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="32" t="n"/>
+      <c r="H52" s="32" t="n"/>
       <c r="I52" s="1" t="n"/>
-      <c r="J52" s="29" t="n">
-        <v>2010</v>
-      </c>
-      <c r="K52" s="30" t="n"/>
-      <c r="L52" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="30" t="n"/>
-      <c r="N52" s="30" t="n"/>
-      <c r="O52" s="30" t="n"/>
-      <c r="P52" s="30" t="n"/>
+      <c r="J52" s="31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K52" s="32" t="n"/>
+      <c r="L52" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="32" t="n"/>
+      <c r="N52" s="32" t="n"/>
+      <c r="O52" s="32" t="n"/>
+      <c r="P52" s="32" t="n"/>
     </row>
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>GTTL</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="13" t="n"/>
+      <c r="B53" s="33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C53" s="34" t="n"/>
+      <c r="D53" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="34" t="n"/>
+      <c r="G53" s="34" t="n"/>
+      <c r="H53" s="34" t="n"/>
       <c r="I53" s="1" t="n"/>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>GTTL</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L53" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="M53" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O53" s="13" t="n"/>
-      <c r="P53" s="13" t="n"/>
+      <c r="J53" s="33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K53" s="34" t="n"/>
+      <c r="L53" s="34" t="n"/>
+      <c r="M53" s="34" t="n"/>
+      <c r="N53" s="34" t="n"/>
+      <c r="O53" s="34" t="n"/>
+      <c r="P53" s="34" t="n"/>
     </row>
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="1" t="n"/>
-      <c r="B54" s="1" t="n"/>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="1" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
+      <c r="B54" s="33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C54" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="34" t="n"/>
+      <c r="E54" s="34" t="n"/>
+      <c r="F54" s="34" t="n"/>
+      <c r="G54" s="34" t="n"/>
+      <c r="H54" s="34" t="n"/>
       <c r="I54" s="1" t="n"/>
-      <c r="J54" s="1" t="n"/>
-      <c r="K54" s="1" t="n"/>
-      <c r="L54" s="1" t="n"/>
-      <c r="M54" s="1" t="n"/>
-      <c r="N54" s="1" t="n"/>
-      <c r="O54" s="1" t="n"/>
-      <c r="P54" s="1" t="n"/>
+      <c r="J54" s="33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K54" s="34" t="n"/>
+      <c r="L54" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="34" t="n"/>
+      <c r="N54" s="34" t="n"/>
+      <c r="O54" s="34" t="n"/>
+      <c r="P54" s="34" t="n"/>
     </row>
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="1" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
+      <c r="B55" s="33" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="34" t="n"/>
+      <c r="E55" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="34" t="n"/>
       <c r="I55" s="1" t="n"/>
-      <c r="J55" s="1" t="n"/>
-      <c r="K55" s="1" t="n"/>
-      <c r="L55" s="1" t="n"/>
-      <c r="M55" s="1" t="n"/>
-      <c r="N55" s="1" t="n"/>
-      <c r="O55" s="1" t="n"/>
-      <c r="P55" s="1" t="n"/>
+      <c r="J55" s="33" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K55" s="34" t="n"/>
+      <c r="L55" s="34" t="n"/>
+      <c r="M55" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="34" t="n"/>
+      <c r="P55" s="34" t="n"/>
     </row>
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="1" t="n"/>
-      <c r="B56" s="31" t="inlineStr">
-        <is>
-          <t>CARGO CLASSIFICATION  (40'RH stock by Built Year, per depot)</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n"/>
-      <c r="D56" s="1" t="n"/>
-      <c r="E56" s="1" t="n"/>
-      <c r="F56" s="1" t="n"/>
-      <c r="G56" s="1" t="n"/>
-      <c r="H56" s="1" t="n"/>
+      <c r="B56" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C56" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="34" t="n"/>
+      <c r="F56" s="34" t="n"/>
+      <c r="G56" s="34" t="n"/>
+      <c r="H56" s="34" t="n"/>
       <c r="I56" s="1" t="n"/>
-      <c r="J56" s="1" t="n"/>
-      <c r="K56" s="1" t="n"/>
-      <c r="L56" s="1" t="n"/>
-      <c r="M56" s="1" t="n"/>
-      <c r="N56" s="1" t="n"/>
-      <c r="O56" s="1" t="n"/>
-      <c r="P56" s="1" t="n"/>
+      <c r="J56" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K56" s="34" t="n"/>
+      <c r="L56" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="34" t="n"/>
+      <c r="O56" s="34" t="n"/>
+      <c r="P56" s="34" t="n"/>
     </row>
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="32" t="inlineStr">
-        <is>
-          <t>BKK27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="C57" s="33" t="n"/>
-      <c r="D57" s="33" t="n"/>
-      <c r="E57" s="1" t="n"/>
-      <c r="F57" s="32" t="inlineStr">
-        <is>
-          <t>BKK27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="G57" s="33" t="n"/>
-      <c r="H57" s="33" t="n"/>
+      <c r="B57" s="33" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C57" s="34" t="n"/>
+      <c r="D57" s="34" t="n"/>
+      <c r="E57" s="34" t="n"/>
+      <c r="F57" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="34" t="n"/>
+      <c r="H57" s="34" t="n"/>
       <c r="I57" s="1" t="n"/>
-      <c r="J57" s="32" t="inlineStr">
-        <is>
-          <t>LCH27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="K57" s="33" t="n"/>
-      <c r="L57" s="33" t="n"/>
-      <c r="M57" s="1" t="n"/>
-      <c r="N57" s="32" t="inlineStr">
-        <is>
-          <t>LCH27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="O57" s="33" t="n"/>
-      <c r="P57" s="33" t="n"/>
+      <c r="J57" s="33" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K57" s="34" t="n"/>
+      <c r="L57" s="34" t="n"/>
+      <c r="M57" s="34" t="n"/>
+      <c r="N57" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" s="34" t="n"/>
+      <c r="P57" s="34" t="n"/>
     </row>
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="1" t="n"/>
-      <c r="B58" s="34">
-        <f>SUM(D36:D41)+SUM(F36:F41)+SUM(H36:H41)</f>
-        <v/>
-      </c>
-      <c r="C58" s="33" t="n"/>
-      <c r="D58" s="33" t="n"/>
-      <c r="E58" s="1" t="n"/>
-      <c r="F58" s="34">
-        <f>SUM(D42:D52)+SUM(F42:F52)+SUM(H42:H52)</f>
-        <v/>
-      </c>
-      <c r="G58" s="33" t="n"/>
-      <c r="H58" s="33" t="n"/>
+      <c r="B58" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="36" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="36" t="n"/>
       <c r="I58" s="1" t="n"/>
-      <c r="J58" s="35">
-        <f>SUM(L36:L41)+SUM(N36:N41)+SUM(P36:P41)</f>
-        <v/>
-      </c>
-      <c r="K58" s="33" t="n"/>
-      <c r="L58" s="33" t="n"/>
-      <c r="M58" s="1" t="n"/>
-      <c r="N58" s="35">
-        <f>SUM(L42:L52)+SUM(N42:N52)+SUM(P42:P52)</f>
-        <v/>
-      </c>
-      <c r="O58" s="33" t="n"/>
-      <c r="P58" s="33" t="n"/>
+      <c r="J58" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K58" s="36" t="n"/>
+      <c r="L58" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="36" t="n"/>
+      <c r="N58" s="36" t="n"/>
+      <c r="O58" s="36" t="n"/>
+      <c r="P58" s="36" t="n"/>
     </row>
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="1" t="n"/>
-      <c r="B59" s="36" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="C59" s="33" t="n"/>
-      <c r="D59" s="33" t="n"/>
-      <c r="E59" s="1" t="n"/>
-      <c r="F59" s="36" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="G59" s="33" t="n"/>
-      <c r="H59" s="33" t="n"/>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>GTTL</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="13" t="n"/>
       <c r="I59" s="1" t="n"/>
-      <c r="J59" s="36" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="K59" s="33" t="n"/>
-      <c r="L59" s="33" t="n"/>
-      <c r="M59" s="1" t="n"/>
-      <c r="N59" s="36" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="O59" s="33" t="n"/>
-      <c r="P59" s="33" t="n"/>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>GTTL</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O59" s="13" t="n"/>
+      <c r="P59" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="H20:K20"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="E40:F40"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H21:H22"/>
-    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="K40:L40"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
@@ -7069,7 +7069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7089,9 +7089,17 @@
         <f>'TOTAL RH'!A1</f>
         <v/>
       </c>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -7118,32 +7126,28 @@
           <t>SHORTFALL ALERT</t>
         </is>
       </c>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
       <c r="E4" s="1" t="n"/>
       <c r="F4" s="39" t="inlineStr">
         <is>
           <t>COMBINED 40'RH STOCK</t>
         </is>
       </c>
-      <c r="G4" s="33" t="n"/>
-      <c r="H4" s="33" t="n"/>
+      <c r="G4" s="23" t="n"/>
+      <c r="H4" s="23" t="n"/>
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="39" t="inlineStr">
         <is>
           <t>COMBINED 40'RH BOOKING</t>
         </is>
       </c>
-      <c r="K4" s="33" t="n"/>
-      <c r="L4" s="33" t="n"/>
+      <c r="K4" s="23" t="n"/>
+      <c r="L4" s="23" t="n"/>
       <c r="M4" s="1" t="n"/>
-      <c r="N4" s="39" t="inlineStr">
-        <is>
-          <t>COMBINED 40'RH BALANCE</t>
-        </is>
-      </c>
-      <c r="O4" s="33" t="n"/>
-      <c r="P4" s="33" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="1" t="n"/>
@@ -7151,29 +7155,26 @@
         <f>MIN('TOTAL RH'!D12,'TOTAL RH'!J12)</f>
         <v/>
       </c>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
       <c r="E5" s="1" t="n"/>
       <c r="F5" s="41">
         <f>'TOTAL RH'!O5</f>
         <v/>
       </c>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="33" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="1" t="n"/>
       <c r="J5" s="41">
         <f>'TOTAL RH'!O10</f>
         <v/>
       </c>
-      <c r="K5" s="33" t="n"/>
-      <c r="L5" s="33" t="n"/>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="23" t="n"/>
       <c r="M5" s="1" t="n"/>
-      <c r="N5" s="40">
-        <f>'TOTAL RH'!O15</f>
-        <v/>
-      </c>
-      <c r="O5" s="33" t="n"/>
-      <c r="P5" s="33" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="1" t="n"/>
@@ -7181,31 +7182,28 @@
         <f>"BKK27/LCH27 40'RH, worse "&amp;'TOTAL RH'!B12</f>
         <v/>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
       <c r="E6" s="1" t="n"/>
       <c r="F6" s="42" t="inlineStr">
         <is>
           <t>BKK27 + LCH27</t>
         </is>
       </c>
-      <c r="G6" s="33" t="n"/>
-      <c r="H6" s="33" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="42" t="inlineStr">
         <is>
           <t>pending + all weeks</t>
         </is>
       </c>
-      <c r="K6" s="33" t="n"/>
-      <c r="L6" s="33" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
       <c r="M6" s="1" t="n"/>
-      <c r="N6" s="42">
-        <f>"pending + all weeks, both depots, "&amp;'TOTAL RH'!B12</f>
-        <v/>
-      </c>
-      <c r="O6" s="33" t="n"/>
-      <c r="P6" s="33" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="1" t="n"/>
@@ -7273,7 +7271,7 @@
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="33" t="n"/>
+      <c r="B10" s="23" t="n"/>
       <c r="C10" s="46" t="inlineStr">
         <is>
           <t>20'RE</t>
@@ -7287,7 +7285,7 @@
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
       <c r="G10" s="1" t="n"/>
-      <c r="H10" s="33" t="n"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="46" t="inlineStr">
         <is>
           <t>20'RE</t>
@@ -7487,33 +7485,15 @@
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="49">
-        <f>'TOTAL RH'!B9</f>
-        <v/>
-      </c>
-      <c r="C16" s="50">
-        <f>'TOTAL RH'!C9</f>
-        <v/>
-      </c>
-      <c r="D16" s="50">
-        <f>'TOTAL RH'!D9</f>
-        <v/>
-      </c>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
-      <c r="H16" s="49">
-        <f>'TOTAL RH'!H9</f>
-        <v/>
-      </c>
-      <c r="I16" s="50">
-        <f>'TOTAL RH'!I9</f>
-        <v/>
-      </c>
-      <c r="J16" s="50">
-        <f>'TOTAL RH'!J9</f>
-        <v/>
-      </c>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
@@ -7523,31 +7503,31 @@
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="51">
-        <f>'TOTAL RH'!B10</f>
-        <v/>
-      </c>
-      <c r="C17" s="52">
-        <f>'TOTAL RH'!C10</f>
-        <v/>
-      </c>
-      <c r="D17" s="63">
-        <f>'TOTAL RH'!D10</f>
+      <c r="B17" s="49">
+        <f>'TOTAL RH'!B9</f>
+        <v/>
+      </c>
+      <c r="C17" s="50">
+        <f>'TOTAL RH'!C9</f>
+        <v/>
+      </c>
+      <c r="D17" s="50">
+        <f>'TOTAL RH'!D9</f>
         <v/>
       </c>
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
-      <c r="H17" s="51">
-        <f>'TOTAL RH'!H10</f>
-        <v/>
-      </c>
-      <c r="I17" s="52">
-        <f>'TOTAL RH'!I10</f>
-        <v/>
-      </c>
-      <c r="J17" s="52">
-        <f>'TOTAL RH'!J10</f>
+      <c r="H17" s="49">
+        <f>'TOTAL RH'!H9</f>
+        <v/>
+      </c>
+      <c r="I17" s="50">
+        <f>'TOTAL RH'!I9</f>
+        <v/>
+      </c>
+      <c r="J17" s="50">
+        <f>'TOTAL RH'!J9</f>
         <v/>
       </c>
       <c r="K17" s="1" t="n"/>
@@ -7559,31 +7539,31 @@
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="49">
-        <f>'TOTAL RH'!B11</f>
-        <v/>
-      </c>
-      <c r="C18" s="50">
-        <f>'TOTAL RH'!C11</f>
-        <v/>
-      </c>
-      <c r="D18" s="50">
-        <f>'TOTAL RH'!D11</f>
+      <c r="B18" s="51">
+        <f>'TOTAL RH'!B10</f>
+        <v/>
+      </c>
+      <c r="C18" s="52">
+        <f>'TOTAL RH'!C10</f>
+        <v/>
+      </c>
+      <c r="D18" s="63">
+        <f>'TOTAL RH'!D10</f>
         <v/>
       </c>
       <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
-      <c r="H18" s="49">
-        <f>'TOTAL RH'!H11</f>
-        <v/>
-      </c>
-      <c r="I18" s="50">
-        <f>'TOTAL RH'!I11</f>
-        <v/>
-      </c>
-      <c r="J18" s="50">
-        <f>'TOTAL RH'!J11</f>
+      <c r="H18" s="51">
+        <f>'TOTAL RH'!H10</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>'TOTAL RH'!I10</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>'TOTAL RH'!J10</f>
         <v/>
       </c>
       <c r="K18" s="1" t="n"/>
@@ -7595,33 +7575,15 @@
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="51">
-        <f>'TOTAL RH'!B12</f>
-        <v/>
-      </c>
-      <c r="C19" s="52">
-        <f>'TOTAL RH'!C12</f>
-        <v/>
-      </c>
-      <c r="D19" s="63">
-        <f>'TOTAL RH'!D12</f>
-        <v/>
-      </c>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
       <c r="E19" s="1" t="n"/>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
-      <c r="H19" s="51">
-        <f>'TOTAL RH'!H12</f>
-        <v/>
-      </c>
-      <c r="I19" s="52">
-        <f>'TOTAL RH'!I12</f>
-        <v/>
-      </c>
-      <c r="J19" s="63">
-        <f>'TOTAL RH'!J12</f>
-        <v/>
-      </c>
+      <c r="H19" s="1" t="n"/>
+      <c r="I19" s="1" t="n"/>
+      <c r="J19" s="1" t="n"/>
       <c r="K19" s="1" t="n"/>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
@@ -7631,15 +7593,33 @@
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="n"/>
+      <c r="B20" s="49">
+        <f>'TOTAL RH'!B11</f>
+        <v/>
+      </c>
+      <c r="C20" s="50">
+        <f>'TOTAL RH'!C11</f>
+        <v/>
+      </c>
+      <c r="D20" s="50">
+        <f>'TOTAL RH'!D11</f>
+        <v/>
+      </c>
       <c r="E20" s="1" t="n"/>
       <c r="F20" s="1" t="n"/>
       <c r="G20" s="1" t="n"/>
-      <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="n"/>
+      <c r="H20" s="49">
+        <f>'TOTAL RH'!H11</f>
+        <v/>
+      </c>
+      <c r="I20" s="50">
+        <f>'TOTAL RH'!I11</f>
+        <v/>
+      </c>
+      <c r="J20" s="50">
+        <f>'TOTAL RH'!J11</f>
+        <v/>
+      </c>
       <c r="K20" s="1" t="n"/>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
@@ -7649,15 +7629,33 @@
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="n"/>
+      <c r="B21" s="51">
+        <f>'TOTAL RH'!B12</f>
+        <v/>
+      </c>
+      <c r="C21" s="52">
+        <f>'TOTAL RH'!C12</f>
+        <v/>
+      </c>
+      <c r="D21" s="63">
+        <f>'TOTAL RH'!D12</f>
+        <v/>
+      </c>
       <c r="E21" s="1" t="n"/>
       <c r="F21" s="1" t="n"/>
       <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="n"/>
+      <c r="H21" s="51">
+        <f>'TOTAL RH'!H12</f>
+        <v/>
+      </c>
+      <c r="I21" s="52">
+        <f>'TOTAL RH'!I12</f>
+        <v/>
+      </c>
+      <c r="J21" s="63">
+        <f>'TOTAL RH'!J12</f>
+        <v/>
+      </c>
       <c r="K21" s="1" t="n"/>
       <c r="L21" s="1" t="n"/>
       <c r="M21" s="1" t="n"/>
@@ -7667,11 +7665,7 @@
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>REMARKS  (AV = move code IED/IEP/IER, DMG = move code OER)</t>
-        </is>
-      </c>
+      <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="n"/>
       <c r="D22" s="1" t="n"/>
       <c r="E22" s="1" t="n"/>
@@ -7689,21 +7683,15 @@
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="44">
-        <f>'TOTAL RH'!B2</f>
-        <v/>
-      </c>
-      <c r="C23" s="61" t="n"/>
-      <c r="D23" s="62" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
       <c r="E23" s="1" t="n"/>
       <c r="F23" s="1" t="n"/>
       <c r="G23" s="1" t="n"/>
-      <c r="H23" s="45">
-        <f>'TOTAL RH'!H2</f>
-        <v/>
-      </c>
-      <c r="I23" s="61" t="n"/>
-      <c r="J23" s="62" t="n"/>
+      <c r="H23" s="1" t="n"/>
+      <c r="I23" s="1" t="n"/>
+      <c r="J23" s="1" t="n"/>
       <c r="K23" s="1" t="n"/>
       <c r="L23" s="1" t="n"/>
       <c r="M23" s="1" t="n"/>
@@ -7713,31 +7701,19 @@
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="33" t="n"/>
-      <c r="C24" s="46" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>REMARKS  (AV = move code IED/IEP/IER, DMG = move code OER)</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
       <c r="E24" s="1" t="n"/>
       <c r="F24" s="1" t="n"/>
       <c r="G24" s="1" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="46" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="J24" s="46" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
+      <c r="H24" s="1" t="n"/>
+      <c r="I24" s="1" t="n"/>
+      <c r="J24" s="1" t="n"/>
       <c r="K24" s="1" t="n"/>
       <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
@@ -7747,35 +7723,21 @@
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>AV</t>
-        </is>
-      </c>
-      <c r="C25" s="50">
-        <f>'TOTAL RH'!C16</f>
-        <v/>
-      </c>
-      <c r="D25" s="50">
-        <f>'TOTAL RH'!D16</f>
-        <v/>
-      </c>
+      <c r="B25" s="44">
+        <f>'TOTAL RH'!B2</f>
+        <v/>
+      </c>
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="62" t="n"/>
       <c r="E25" s="1" t="n"/>
       <c r="F25" s="1" t="n"/>
       <c r="G25" s="1" t="n"/>
-      <c r="H25" s="33" t="inlineStr">
-        <is>
-          <t>AV</t>
-        </is>
-      </c>
-      <c r="I25" s="50">
-        <f>'TOTAL RH'!I16</f>
-        <v/>
-      </c>
-      <c r="J25" s="50">
-        <f>'TOTAL RH'!J16</f>
-        <v/>
-      </c>
+      <c r="H25" s="45">
+        <f>'TOTAL RH'!H2</f>
+        <v/>
+      </c>
+      <c r="I25" s="61" t="n"/>
+      <c r="J25" s="62" t="n"/>
       <c r="K25" s="1" t="n"/>
       <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
@@ -7785,34 +7747,30 @@
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>DMG</t>
-        </is>
-      </c>
-      <c r="C26" s="50">
-        <f>'TOTAL RH'!C17</f>
-        <v/>
-      </c>
-      <c r="D26" s="50">
-        <f>'TOTAL RH'!D17</f>
-        <v/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
       </c>
       <c r="E26" s="1" t="n"/>
       <c r="F26" s="1" t="n"/>
       <c r="G26" s="1" t="n"/>
-      <c r="H26" s="33" t="inlineStr">
-        <is>
-          <t>DMG</t>
-        </is>
-      </c>
-      <c r="I26" s="50">
-        <f>'TOTAL RH'!I17</f>
-        <v/>
-      </c>
-      <c r="J26" s="50">
-        <f>'TOTAL RH'!J17</f>
-        <v/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="46" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="J26" s="46" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
       </c>
       <c r="K26" s="1" t="n"/>
       <c r="L26" s="1" t="n"/>
@@ -7823,15 +7781,35 @@
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="C27" s="50">
+        <f>'TOTAL RH'!C16</f>
+        <v/>
+      </c>
+      <c r="D27" s="50">
+        <f>'TOTAL RH'!D16</f>
+        <v/>
+      </c>
       <c r="E27" s="1" t="n"/>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="n"/>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="I27" s="50">
+        <f>'TOTAL RH'!I16</f>
+        <v/>
+      </c>
+      <c r="J27" s="50">
+        <f>'TOTAL RH'!J16</f>
+        <v/>
+      </c>
       <c r="K27" s="1" t="n"/>
       <c r="L27" s="1" t="n"/>
       <c r="M27" s="1" t="n"/>
@@ -7841,15 +7819,35 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>DMG</t>
+        </is>
+      </c>
+      <c r="C28" s="50">
+        <f>'TOTAL RH'!C17</f>
+        <v/>
+      </c>
+      <c r="D28" s="50">
+        <f>'TOTAL RH'!D17</f>
+        <v/>
+      </c>
       <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="n"/>
       <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="n"/>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>DMG</t>
+        </is>
+      </c>
+      <c r="I28" s="50">
+        <f>'TOTAL RH'!I17</f>
+        <v/>
+      </c>
+      <c r="J28" s="50">
+        <f>'TOTAL RH'!J17</f>
+        <v/>
+      </c>
       <c r="K28" s="1" t="n"/>
       <c r="L28" s="1" t="n"/>
       <c r="M28" s="1" t="n"/>
@@ -7859,11 +7857,7 @@
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="43" t="inlineStr">
-        <is>
-          <t>RF SEASONAL — build year</t>
-        </is>
-      </c>
+      <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="n"/>
       <c r="D29" s="1" t="n"/>
       <c r="E29" s="1" t="n"/>
@@ -7881,29 +7875,17 @@
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>BKK27 2020-26 BUILT</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="n"/>
+      <c r="D30" s="1" t="n"/>
       <c r="E30" s="1" t="n"/>
-      <c r="F30" s="39" t="inlineStr">
-        <is>
-          <t>LCH27 2020-26 BUILT</t>
-        </is>
-      </c>
-      <c r="G30" s="33" t="n"/>
-      <c r="H30" s="33" t="n"/>
+      <c r="F30" s="1" t="n"/>
+      <c r="G30" s="1" t="n"/>
+      <c r="H30" s="1" t="n"/>
       <c r="I30" s="1" t="n"/>
-      <c r="J30" s="39" t="inlineStr">
-        <is>
-          <t>PEAK BUILD YEAR</t>
-        </is>
-      </c>
-      <c r="K30" s="33" t="n"/>
-      <c r="L30" s="33" t="n"/>
+      <c r="J30" s="1" t="n"/>
+      <c r="K30" s="1" t="n"/>
+      <c r="L30" s="1" t="n"/>
       <c r="M30" s="1" t="n"/>
       <c r="N30" s="1" t="n"/>
       <c r="O30" s="1" t="n"/>
@@ -7911,26 +7893,21 @@
     </row>
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="53">
-        <f>SUM('TOTAL RH'!D36:D42)+SUM('TOTAL RH'!F36:F42)+SUM('TOTAL RH'!H36:H42)</f>
-        <v/>
-      </c>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>RF SEASONAL — build year</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n"/>
+      <c r="D31" s="1" t="n"/>
       <c r="E31" s="1" t="n"/>
-      <c r="F31" s="54">
-        <f>SUM('TOTAL RH'!L36:L42)+SUM('TOTAL RH'!N36:N42)+SUM('TOTAL RH'!P36:P42)</f>
-        <v/>
-      </c>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="1" t="n"/>
+      <c r="H31" s="1" t="n"/>
       <c r="I31" s="1" t="n"/>
-      <c r="J31" s="41">
-        <f>"2021"</f>
-        <v/>
-      </c>
-      <c r="K31" s="33" t="n"/>
-      <c r="L31" s="33" t="n"/>
+      <c r="J31" s="1" t="n"/>
+      <c r="K31" s="1" t="n"/>
+      <c r="L31" s="1" t="n"/>
       <c r="M31" s="1" t="n"/>
       <c r="N31" s="1" t="n"/>
       <c r="O31" s="1" t="n"/>
@@ -7938,29 +7915,29 @@
     </row>
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="42" t="inlineStr">
-        <is>
-          <t>of 40'RH on hand</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="33" t="n"/>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>BKK27 2020-26 BUILT</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
       <c r="E32" s="1" t="n"/>
-      <c r="F32" s="42" t="inlineStr">
-        <is>
-          <t>of 40'RH on hand</t>
-        </is>
-      </c>
-      <c r="G32" s="33" t="n"/>
-      <c r="H32" s="33" t="n"/>
+      <c r="F32" s="39" t="inlineStr">
+        <is>
+          <t>LCH27 2020-26 BUILT</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="n"/>
       <c r="I32" s="1" t="n"/>
-      <c r="J32" s="42" t="inlineStr">
-        <is>
-          <t>17 units across both depots</t>
-        </is>
-      </c>
-      <c r="K32" s="33" t="n"/>
-      <c r="L32" s="33" t="n"/>
+      <c r="J32" s="39" t="inlineStr">
+        <is>
+          <t>PEAK BUILD YEAR</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="23" t="n"/>
       <c r="M32" s="1" t="n"/>
       <c r="N32" s="1" t="n"/>
       <c r="O32" s="1" t="n"/>
@@ -7968,17 +7945,26 @@
     </row>
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
-      <c r="C33" s="1" t="n"/>
-      <c r="D33" s="1" t="n"/>
+      <c r="B33" s="53">
+        <f>SUM('TOTAL RH'!D42:D48)+SUM('TOTAL RH'!F42:F48)+SUM('TOTAL RH'!H42:H48)</f>
+        <v/>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
       <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="n"/>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="1" t="n"/>
+      <c r="F33" s="54">
+        <f>SUM('TOTAL RH'!L42:L48)+SUM('TOTAL RH'!N42:N48)+SUM('TOTAL RH'!P42:P48)</f>
+        <v/>
+      </c>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
       <c r="I33" s="1" t="n"/>
-      <c r="J33" s="1" t="n"/>
-      <c r="K33" s="1" t="n"/>
-      <c r="L33" s="1" t="n"/>
+      <c r="J33" s="41">
+        <f>"2021"</f>
+        <v/>
+      </c>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
       <c r="M33" s="1" t="n"/>
       <c r="N33" s="1" t="n"/>
       <c r="O33" s="1" t="n"/>
@@ -7986,173 +7972,161 @@
     </row>
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>BKK27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>of 40'RH on hand</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
       <c r="E34" s="1" t="n"/>
-      <c r="F34" s="39" t="inlineStr">
-        <is>
-          <t>BKK27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
+      <c r="F34" s="42" t="inlineStr">
+        <is>
+          <t>of 40'RH on hand</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
       <c r="I34" s="1" t="n"/>
-      <c r="J34" s="39" t="inlineStr">
-        <is>
-          <t>LCH27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="K34" s="33" t="n"/>
-      <c r="L34" s="33" t="n"/>
+      <c r="J34" s="42" t="inlineStr">
+        <is>
+          <t>17 units across both depots</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n"/>
+      <c r="L34" s="23" t="n"/>
       <c r="M34" s="1" t="n"/>
-      <c r="N34" s="39" t="inlineStr">
-        <is>
-          <t>LCH27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="O34" s="33" t="n"/>
-      <c r="P34" s="33" t="n"/>
+      <c r="N34" s="1" t="n"/>
+      <c r="O34" s="1" t="n"/>
+      <c r="P34" s="1" t="n"/>
     </row>
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="53">
-        <f>'TOTAL RH'!B58</f>
-        <v/>
-      </c>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="1" t="n"/>
       <c r="E35" s="1" t="n"/>
-      <c r="F35" s="53">
-        <f>'TOTAL RH'!F58</f>
-        <v/>
-      </c>
-      <c r="G35" s="33" t="n"/>
-      <c r="H35" s="33" t="n"/>
+      <c r="F35" s="1" t="n"/>
+      <c r="G35" s="1" t="n"/>
+      <c r="H35" s="1" t="n"/>
       <c r="I35" s="1" t="n"/>
-      <c r="J35" s="54">
-        <f>'TOTAL RH'!J58</f>
-        <v/>
-      </c>
-      <c r="K35" s="33" t="n"/>
-      <c r="L35" s="33" t="n"/>
+      <c r="J35" s="1" t="n"/>
+      <c r="K35" s="1" t="n"/>
+      <c r="L35" s="1" t="n"/>
       <c r="M35" s="1" t="n"/>
-      <c r="N35" s="54">
-        <f>'TOTAL RH'!N58</f>
-        <v/>
-      </c>
-      <c r="O35" s="33" t="n"/>
-      <c r="P35" s="33" t="n"/>
+      <c r="N35" s="1" t="n"/>
+      <c r="O35" s="1" t="n"/>
+      <c r="P35" s="1" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="42" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n"/>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>BKK27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
       <c r="E36" s="1" t="n"/>
-      <c r="F36" s="42" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="G36" s="33" t="n"/>
-      <c r="H36" s="33" t="n"/>
+      <c r="F36" s="39" t="inlineStr">
+        <is>
+          <t>BKK27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
       <c r="I36" s="1" t="n"/>
-      <c r="J36" s="42" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="K36" s="33" t="n"/>
-      <c r="L36" s="33" t="n"/>
+      <c r="J36" s="39" t="inlineStr">
+        <is>
+          <t>LCH27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n"/>
+      <c r="L36" s="23" t="n"/>
       <c r="M36" s="1" t="n"/>
-      <c r="N36" s="42" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="O36" s="33" t="n"/>
-      <c r="P36" s="33" t="n"/>
+      <c r="N36" s="39" t="inlineStr">
+        <is>
+          <t>LCH27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="O36" s="23" t="n"/>
+      <c r="P36" s="23" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
+      <c r="B37" s="53">
+        <f>'TOTAL RH'!B35</f>
+        <v/>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
       <c r="E37" s="1" t="n"/>
-      <c r="F37" s="1" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="n"/>
+      <c r="F37" s="53">
+        <f>'TOTAL RH'!F35</f>
+        <v/>
+      </c>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
       <c r="I37" s="1" t="n"/>
-      <c r="J37" s="1" t="n"/>
-      <c r="K37" s="1" t="n"/>
-      <c r="L37" s="1" t="n"/>
+      <c r="J37" s="54">
+        <f>'TOTAL RH'!J35</f>
+        <v/>
+      </c>
+      <c r="K37" s="23" t="n"/>
+      <c r="L37" s="23" t="n"/>
       <c r="M37" s="1" t="n"/>
-      <c r="N37" s="1" t="n"/>
-      <c r="O37" s="1" t="n"/>
-      <c r="P37" s="1" t="n"/>
+      <c r="N37" s="54">
+        <f>'TOTAL RH'!N35</f>
+        <v/>
+      </c>
+      <c r="O37" s="23" t="n"/>
+      <c r="P37" s="23" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>BKK27 current mix</t>
-        </is>
-      </c>
-      <c r="C38" s="61" t="n"/>
-      <c r="D38" s="62" t="n"/>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
       <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="45" t="inlineStr">
-        <is>
-          <t>LCH27 current mix</t>
-        </is>
-      </c>
-      <c r="I38" s="61" t="n"/>
-      <c r="J38" s="62" t="n"/>
-      <c r="K38" s="1" t="n"/>
-      <c r="L38" s="1" t="n"/>
+      <c r="F38" s="42" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="1" t="n"/>
+      <c r="J38" s="42" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="n"/>
+      <c r="L38" s="23" t="n"/>
       <c r="M38" s="1" t="n"/>
-      <c r="N38" s="1" t="n"/>
-      <c r="O38" s="1" t="n"/>
-      <c r="P38" s="1" t="n"/>
+      <c r="N38" s="42" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="O38" s="23" t="n"/>
+      <c r="P38" s="23" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="33" t="n"/>
-      <c r="C39" s="46" t="inlineStr">
-        <is>
-          <t>22RE</t>
-        </is>
-      </c>
-      <c r="D39" s="46" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="n"/>
+      <c r="D39" s="1" t="n"/>
       <c r="E39" s="1" t="n"/>
       <c r="F39" s="1" t="n"/>
       <c r="G39" s="1" t="n"/>
-      <c r="H39" s="33" t="n"/>
-      <c r="I39" s="46" t="inlineStr">
-        <is>
-          <t>22RE</t>
-        </is>
-      </c>
-      <c r="J39" s="46" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="H39" s="1" t="n"/>
+      <c r="I39" s="1" t="n"/>
+      <c r="J39" s="1" t="n"/>
       <c r="K39" s="1" t="n"/>
       <c r="L39" s="1" t="n"/>
       <c r="M39" s="1" t="n"/>
@@ -8162,35 +8136,23 @@
     </row>
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="C40" s="50">
-        <f>'TOTAL RH'!C53</f>
-        <v/>
-      </c>
-      <c r="D40" s="50">
-        <f>'TOTAL RH'!D53</f>
-        <v/>
-      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>BKK27 current mix</t>
+        </is>
+      </c>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="62" t="n"/>
       <c r="E40" s="1" t="n"/>
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
-      <c r="H40" s="33" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="I40" s="50">
-        <f>'TOTAL RH'!K53</f>
-        <v/>
-      </c>
-      <c r="J40" s="50">
-        <f>'TOTAL RH'!L53</f>
-        <v/>
-      </c>
+      <c r="H40" s="45" t="inlineStr">
+        <is>
+          <t>LCH27 current mix</t>
+        </is>
+      </c>
+      <c r="I40" s="61" t="n"/>
+      <c r="J40" s="62" t="n"/>
       <c r="K40" s="1" t="n"/>
       <c r="L40" s="1" t="n"/>
       <c r="M40" s="1" t="n"/>
@@ -8200,34 +8162,30 @@
     </row>
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="C41" s="50">
-        <f>'TOTAL RH'!E53</f>
-        <v/>
-      </c>
-      <c r="D41" s="50">
-        <f>'TOTAL RH'!F53</f>
-        <v/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>22RE</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
       <c r="E41" s="1" t="n"/>
       <c r="F41" s="1" t="n"/>
       <c r="G41" s="1" t="n"/>
-      <c r="H41" s="33" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="I41" s="50">
-        <f>'TOTAL RH'!M53</f>
-        <v/>
-      </c>
-      <c r="J41" s="50">
-        <f>'TOTAL RH'!N53</f>
-        <v/>
+      <c r="H41" s="23" t="n"/>
+      <c r="I41" s="46" t="inlineStr">
+        <is>
+          <t>22RE</t>
+        </is>
+      </c>
+      <c r="J41" s="46" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
       <c r="K41" s="1" t="n"/>
       <c r="L41" s="1" t="n"/>
@@ -8238,33 +8196,33 @@
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
         </is>
       </c>
       <c r="C42" s="50">
-        <f>'TOTAL RH'!G53</f>
+        <f>'TOTAL RH'!C59</f>
         <v/>
       </c>
       <c r="D42" s="50">
-        <f>'TOTAL RH'!H53</f>
+        <f>'TOTAL RH'!D59</f>
         <v/>
       </c>
       <c r="E42" s="1" t="n"/>
       <c r="F42" s="1" t="n"/>
       <c r="G42" s="1" t="n"/>
-      <c r="H42" s="33" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
         </is>
       </c>
       <c r="I42" s="50">
-        <f>'TOTAL RH'!O53</f>
+        <f>'TOTAL RH'!K59</f>
         <v/>
       </c>
       <c r="J42" s="50">
-        <f>'TOTAL RH'!P53</f>
+        <f>'TOTAL RH'!L59</f>
         <v/>
       </c>
       <c r="K42" s="1" t="n"/>
@@ -8276,15 +8234,35 @@
     </row>
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="C43" s="50">
+        <f>'TOTAL RH'!E59</f>
+        <v/>
+      </c>
+      <c r="D43" s="50">
+        <f>'TOTAL RH'!F59</f>
+        <v/>
+      </c>
       <c r="E43" s="1" t="n"/>
       <c r="F43" s="1" t="n"/>
       <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="1" t="n"/>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="I43" s="50">
+        <f>'TOTAL RH'!M59</f>
+        <v/>
+      </c>
+      <c r="J43" s="50">
+        <f>'TOTAL RH'!N59</f>
+        <v/>
+      </c>
       <c r="K43" s="1" t="n"/>
       <c r="L43" s="1" t="n"/>
       <c r="M43" s="1" t="n"/>
@@ -8294,19 +8272,35 @@
     </row>
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="55" t="inlineStr">
-        <is>
-          <t>Full 2010-2026 Year x Brand x Size breakdown is on the TOTAL RH sheet.</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="n"/>
-      <c r="D44" s="1" t="n"/>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
+      </c>
+      <c r="C44" s="50">
+        <f>'TOTAL RH'!G59</f>
+        <v/>
+      </c>
+      <c r="D44" s="50">
+        <f>'TOTAL RH'!H59</f>
+        <v/>
+      </c>
       <c r="E44" s="1" t="n"/>
       <c r="F44" s="1" t="n"/>
       <c r="G44" s="1" t="n"/>
-      <c r="H44" s="1" t="n"/>
-      <c r="I44" s="1" t="n"/>
-      <c r="J44" s="1" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
+      </c>
+      <c r="I44" s="50">
+        <f>'TOTAL RH'!O59</f>
+        <v/>
+      </c>
+      <c r="J44" s="50">
+        <f>'TOTAL RH'!P59</f>
+        <v/>
+      </c>
       <c r="K44" s="1" t="n"/>
       <c r="L44" s="1" t="n"/>
       <c r="M44" s="1" t="n"/>
@@ -8314,15 +8308,55 @@
       <c r="O44" s="1" t="n"/>
       <c r="P44" s="1" t="n"/>
     </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n"/>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="n"/>
+      <c r="G45" s="1" t="n"/>
+      <c r="H45" s="1" t="n"/>
+      <c r="I45" s="1" t="n"/>
+      <c r="J45" s="1" t="n"/>
+      <c r="K45" s="1" t="n"/>
+      <c r="L45" s="1" t="n"/>
+      <c r="M45" s="1" t="n"/>
+      <c r="N45" s="1" t="n"/>
+      <c r="O45" s="1" t="n"/>
+      <c r="P45" s="1" t="n"/>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>Full 2010-2026 Year x Brand x Size breakdown is on the TOTAL RH sheet.</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n"/>
+      <c r="D46" s="1" t="n"/>
+      <c r="E46" s="1" t="n"/>
+      <c r="F46" s="1" t="n"/>
+      <c r="G46" s="1" t="n"/>
+      <c r="H46" s="1" t="n"/>
+      <c r="I46" s="1" t="n"/>
+      <c r="J46" s="1" t="n"/>
+      <c r="K46" s="1" t="n"/>
+      <c r="L46" s="1" t="n"/>
+      <c r="M46" s="1" t="n"/>
+      <c r="N46" s="1" t="n"/>
+      <c r="O46" s="1" t="n"/>
+      <c r="P46" s="1" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="B1:P2"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B1:L2"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H9:J9"/>
-    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="H25:J25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
